--- a/experiments/results/resnet18/CIFAR-10/ReAct/adaptive/max/results.xlsx
+++ b/experiments/results/resnet18/CIFAR-10/ReAct/adaptive/max/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -1009,6 +1009,104 @@
       <c r="O13" s="5" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=0.4,scale_th=3.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>98.45999999999999</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>93.64</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>98.45</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>97.62</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>99.61</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>98.47</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>97.70999999999999</v>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=0.4,scale_th=10.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>34.77</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>93.47</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>98.39</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>97.51000000000001</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>99.63</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>98.41</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>97.64</v>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=0.5,scale_th=10.0,type=max</t>
         </is>
       </c>
     </row>
